--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15.72</v>
+        <v>689.64</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>841.936</v>
+        <v>36935.71</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>241.34</v>
+        <v>10587.58</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>211.721</v>
+        <v>9288.200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -813,11 +813,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13164.00002492</v>
+        <v>577504.36</v>
       </c>
     </row>
     <row r="7">
@@ -874,11 +874,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37.298</v>
+        <v>1636.26</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>160.162</v>
+        <v>7026.3</v>
       </c>
     </row>
     <row r="9">
@@ -1000,11 +1000,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3527.952</v>
+        <v>154771.17</v>
       </c>
     </row>
     <row r="10">
@@ -1065,11 +1065,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>440.994</v>
+        <v>19346.4</v>
       </c>
     </row>
     <row r="11">
@@ -1126,11 +1126,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26.999</v>
+        <v>1184.45</v>
       </c>
     </row>
     <row r="12">
@@ -1187,11 +1187,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>239.146</v>
+        <v>10491.33</v>
       </c>
     </row>
     <row r="13">
@@ -1252,11 +1252,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>32049.936</v>
+        <v>1406029.91</v>
       </c>
     </row>
     <row r="14">
@@ -1313,11 +1313,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>177.714</v>
+        <v>7796.31</v>
       </c>
     </row>
     <row r="15">
@@ -1374,11 +1374,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>828.235</v>
+        <v>36334.65</v>
       </c>
     </row>
     <row r="16">
@@ -1435,11 +1435,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>840.894</v>
+        <v>36890</v>
       </c>
     </row>
   </sheetData>
